--- a/output/BUSINESS_METRICS.xlsx
+++ b/output/BUSINESS_METRICS.xlsx
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/output/BUSINESS_METRICS.xlsx
+++ b/output/BUSINESS_METRICS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>96</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8">
@@ -501,11 +501,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>STOCK out of scope</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Duration sec</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>99</v>
+      <c r="B10" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
